--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU10/HRM/post FET_HRM-2031-0232/Panel-28/front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU10_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU10/HRM/post FET_HRM-2031-0232/Panel-28/front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU10_Front_Summary.xlsx
@@ -434,25 +434,15 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Outer Radius</t>
+          <t>Radius</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Inner Radius</t>
+          <t>Dimple</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
-        <is>
-          <t>Diameter</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Dimple</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
         <is>
           <t>Bump</t>
         </is>
@@ -470,28 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>18.13507</v>
+        <v>17.68012</v>
       </c>
       <c r="D2" t="n">
-        <v>17.55627</v>
+        <v>17.13458</v>
       </c>
       <c r="E2" t="n">
-        <v>17.71953</v>
+        <v>17.58933</v>
       </c>
       <c r="F2" t="n">
-        <v>57.25823</v>
+        <v>45.50384</v>
       </c>
       <c r="G2" t="n">
-        <v>43.93534</v>
+        <v>0.0528</v>
       </c>
       <c r="H2" t="n">
-        <v>88.71245</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0.05261</v>
-      </c>
-      <c r="J2" t="n">
-        <v>1.90607</v>
+        <v>1.91343</v>
       </c>
     </row>
     <row r="3">
@@ -501,28 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>18.07048</v>
+        <v>18.02246</v>
       </c>
       <c r="D3" t="n">
-        <v>17.36442</v>
+        <v>17.45182</v>
       </c>
       <c r="E3" t="n">
-        <v>17.73925</v>
+        <v>17.79432</v>
       </c>
       <c r="F3" t="n">
-        <v>59.32518</v>
+        <v>44.68122</v>
       </c>
       <c r="G3" t="n">
-        <v>44.35076</v>
+        <v>0.05319</v>
       </c>
       <c r="H3" t="n">
-        <v>89.45371</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0.05274</v>
-      </c>
-      <c r="J3" t="n">
-        <v>1.94257</v>
+        <v>1.88209</v>
       </c>
     </row>
     <row r="4">
@@ -532,28 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17.37492</v>
+        <v>17.52595</v>
       </c>
       <c r="D4" t="n">
-        <v>17.56116</v>
+        <v>17.11241</v>
       </c>
       <c r="E4" t="n">
-        <v>17.45493</v>
+        <v>17.40015</v>
       </c>
       <c r="F4" t="n">
-        <v>58.73952</v>
+        <v>44.99788</v>
       </c>
       <c r="G4" t="n">
-        <v>45.74084</v>
+        <v>0.05319</v>
       </c>
       <c r="H4" t="n">
-        <v>92.14261</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0.05394</v>
-      </c>
-      <c r="J4" t="n">
-        <v>1.94136</v>
+        <v>1.96584</v>
       </c>
     </row>
     <row r="5">
@@ -563,28 +535,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>17.66906</v>
+        <v>17.61824</v>
       </c>
       <c r="D5" t="n">
-        <v>17.64161</v>
+        <v>17.43877</v>
       </c>
       <c r="E5" t="n">
-        <v>17.57482</v>
+        <v>17.45877</v>
       </c>
       <c r="F5" t="n">
-        <v>57.53379</v>
+        <v>44.77495</v>
       </c>
       <c r="G5" t="n">
-        <v>45.54335</v>
+        <v>0.05343</v>
       </c>
       <c r="H5" t="n">
-        <v>87.96258</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0.05157</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1.93577</v>
+        <v>1.92599</v>
       </c>
     </row>
     <row r="6">
@@ -594,28 +560,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>17.83686</v>
+        <v>17.63731</v>
       </c>
       <c r="D6" t="n">
-        <v>17.49995</v>
+        <v>17.4586</v>
       </c>
       <c r="E6" t="n">
-        <v>17.02366</v>
+        <v>17.49201</v>
       </c>
       <c r="F6" t="n">
-        <v>59.34292</v>
+        <v>43.7645</v>
       </c>
       <c r="G6" t="n">
-        <v>43.759</v>
+        <v>0.05195</v>
       </c>
       <c r="H6" t="n">
-        <v>89.12184000000001</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0.05206</v>
-      </c>
-      <c r="J6" t="n">
-        <v>1.94502</v>
+        <v>1.90226</v>
       </c>
     </row>
     <row r="7">
@@ -625,28 +585,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>17.71006</v>
+        <v>17.63544</v>
       </c>
       <c r="D7" t="n">
-        <v>17.54663</v>
+        <v>16.84083</v>
       </c>
       <c r="E7" t="n">
-        <v>17.45263</v>
+        <v>17.61932</v>
       </c>
       <c r="F7" t="n">
-        <v>58.8601</v>
+        <v>44.72867</v>
       </c>
       <c r="G7" t="n">
-        <v>44.78007</v>
+        <v>0.05292</v>
       </c>
       <c r="H7" t="n">
-        <v>87.75423000000001</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0.05223</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1.90054</v>
+        <v>1.92338</v>
       </c>
     </row>
     <row r="8">
@@ -656,28 +610,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.6186</v>
+        <v>18.13507</v>
       </c>
       <c r="D8" t="n">
-        <v>17.62194</v>
+        <v>17.55627</v>
       </c>
       <c r="E8" t="n">
-        <v>17.64461</v>
+        <v>17.71953</v>
       </c>
       <c r="F8" t="n">
-        <v>59.28689</v>
+        <v>43.72447</v>
       </c>
       <c r="G8" t="n">
-        <v>44.30495</v>
+        <v>0.0523</v>
       </c>
       <c r="H8" t="n">
-        <v>88.74315</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0.05262</v>
-      </c>
-      <c r="J8" t="n">
-        <v>1.89842</v>
+        <v>1.90098</v>
       </c>
     </row>
     <row r="9">
@@ -687,28 +635,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>17.67045</v>
+        <v>17.96162</v>
       </c>
       <c r="D9" t="n">
-        <v>17.28287</v>
+        <v>17.36645</v>
       </c>
       <c r="E9" t="n">
-        <v>17.44756</v>
+        <v>17.46734</v>
       </c>
       <c r="F9" t="n">
-        <v>58.30447</v>
+        <v>44.46987</v>
       </c>
       <c r="G9" t="n">
-        <v>44.13406</v>
+        <v>0.05376</v>
       </c>
       <c r="H9" t="n">
-        <v>91.13751000000001</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.05298</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1.93657</v>
+        <v>1.94155</v>
       </c>
     </row>
     <row r="10">
@@ -718,28 +660,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>17.19633</v>
+        <v>17.52911</v>
       </c>
       <c r="D10" t="n">
-        <v>17.55471</v>
+        <v>17.40301</v>
       </c>
       <c r="E10" t="n">
-        <v>17.48106</v>
+        <v>17.46477</v>
       </c>
       <c r="F10" t="n">
-        <v>58.74277</v>
+        <v>45.32673</v>
       </c>
       <c r="G10" t="n">
-        <v>43.93231</v>
+        <v>0.05233</v>
       </c>
       <c r="H10" t="n">
-        <v>90.26891000000001</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0.05319</v>
-      </c>
-      <c r="J10" t="n">
-        <v>1.92365</v>
+        <v>1.92744</v>
       </c>
     </row>
     <row r="11">
@@ -760,25 +696,15 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Outer Radius</t>
+          <t>Radius</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Inner Radius</t>
+          <t>Dimple</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
-        <is>
-          <t>Diameter</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Dimple</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
         <is>
           <t>Bump</t>
         </is>
@@ -792,32 +718,26 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Pad 2</t>
+          <t>Pad 1</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>17.70638</v>
+        <v>17.96962</v>
       </c>
       <c r="D12" t="n">
-        <v>17.62788</v>
+        <v>17.51506</v>
       </c>
       <c r="E12" t="n">
-        <v>17.25935</v>
+        <v>17.56071</v>
       </c>
       <c r="F12" t="n">
-        <v>57.76934</v>
+        <v>46.0713</v>
       </c>
       <c r="G12" t="n">
-        <v>44.14523</v>
+        <v>0.05394</v>
       </c>
       <c r="H12" t="n">
-        <v>89.32196</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0.05301</v>
-      </c>
-      <c r="J12" t="n">
-        <v>1.90913</v>
+        <v>1.94136</v>
       </c>
     </row>
     <row r="13">
@@ -827,28 +747,22 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>17.83086</v>
+        <v>17.66906</v>
       </c>
       <c r="D13" t="n">
-        <v>17.6764</v>
+        <v>17.57482</v>
       </c>
       <c r="E13" t="n">
-        <v>17.32705</v>
+        <v>17.64161</v>
       </c>
       <c r="F13" t="n">
-        <v>57.30218</v>
+        <v>43.93489</v>
       </c>
       <c r="G13" t="n">
-        <v>43.51386</v>
+        <v>0.05422</v>
       </c>
       <c r="H13" t="n">
-        <v>89.58132999999999</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0.05229</v>
-      </c>
-      <c r="J13" t="n">
-        <v>1.87834</v>
+        <v>1.88491</v>
       </c>
     </row>
     <row r="14">
@@ -858,28 +772,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>17.6336</v>
+        <v>17.72941</v>
       </c>
       <c r="D14" t="n">
-        <v>17.5081</v>
+        <v>17.1212</v>
       </c>
       <c r="E14" t="n">
-        <v>17.33644</v>
+        <v>17.63704</v>
       </c>
       <c r="F14" t="n">
-        <v>58.54498</v>
+        <v>44.81693</v>
       </c>
       <c r="G14" t="n">
-        <v>44.79676</v>
+        <v>0.05159</v>
       </c>
       <c r="H14" t="n">
-        <v>87.98679</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0.0531</v>
-      </c>
-      <c r="J14" t="n">
-        <v>1.91661</v>
+        <v>1.94213</v>
       </c>
     </row>
     <row r="15">
@@ -889,28 +797,22 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>17.91379</v>
+        <v>17.39998</v>
       </c>
       <c r="D15" t="n">
-        <v>17.04245</v>
+        <v>17.18111</v>
       </c>
       <c r="E15" t="n">
-        <v>17.28038</v>
+        <v>17.29522</v>
       </c>
       <c r="F15" t="n">
-        <v>59.24192</v>
+        <v>45.3837</v>
       </c>
       <c r="G15" t="n">
-        <v>45.39536</v>
+        <v>0.05334</v>
       </c>
       <c r="H15" t="n">
-        <v>88.39006000000001</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0.05295</v>
-      </c>
-      <c r="J15" t="n">
-        <v>1.93511</v>
+        <v>1.92585</v>
       </c>
     </row>
     <row r="16">
@@ -920,28 +822,22 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>17.31753</v>
+        <v>17.59217</v>
       </c>
       <c r="D16" t="n">
-        <v>17.21631</v>
+        <v>17.55101</v>
       </c>
       <c r="E16" t="n">
-        <v>17.65287</v>
+        <v>17.55841</v>
       </c>
       <c r="F16" t="n">
-        <v>58.08381</v>
+        <v>43.87711</v>
       </c>
       <c r="G16" t="n">
-        <v>44.88482</v>
+        <v>0.05223</v>
       </c>
       <c r="H16" t="n">
-        <v>89.5218</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0.05246</v>
-      </c>
-      <c r="J16" t="n">
-        <v>1.89055</v>
+        <v>1.90054</v>
       </c>
     </row>
     <row r="17">
@@ -951,28 +847,22 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>17.63428</v>
+        <v>17.64461</v>
       </c>
       <c r="D17" t="n">
-        <v>17.13857</v>
+        <v>17.6186</v>
       </c>
       <c r="E17" t="n">
-        <v>17.40042</v>
+        <v>17.62194</v>
       </c>
       <c r="F17" t="n">
-        <v>57.70048</v>
+        <v>45.27362</v>
       </c>
       <c r="G17" t="n">
-        <v>44.24639</v>
+        <v>0.05274</v>
       </c>
       <c r="H17" t="n">
-        <v>88.41589999999999</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0.05246</v>
-      </c>
-      <c r="J17" t="n">
-        <v>1.92414</v>
+        <v>1.90164</v>
       </c>
     </row>
     <row r="18">
@@ -982,28 +872,22 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>17.69047</v>
+        <v>17.564</v>
       </c>
       <c r="D18" t="n">
-        <v>17.07247</v>
+        <v>17.29675</v>
       </c>
       <c r="E18" t="n">
-        <v>17.8638</v>
+        <v>17.47102</v>
       </c>
       <c r="F18" t="n">
-        <v>58.145</v>
+        <v>44.26102</v>
       </c>
       <c r="G18" t="n">
-        <v>43.4423</v>
+        <v>0.05287</v>
       </c>
       <c r="H18" t="n">
-        <v>88.50125</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0.05301</v>
-      </c>
-      <c r="J18" t="n">
-        <v>1.96498</v>
+        <v>1.90815</v>
       </c>
     </row>
     <row r="19">
@@ -1013,28 +897,22 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>17.60691</v>
+        <v>17.79351</v>
       </c>
       <c r="D19" t="n">
-        <v>17.47049</v>
+        <v>17.44346</v>
       </c>
       <c r="E19" t="n">
-        <v>17.78968</v>
+        <v>17.48494</v>
       </c>
       <c r="F19" t="n">
-        <v>59.05676</v>
+        <v>45.18658</v>
       </c>
       <c r="G19" t="n">
-        <v>44.92454</v>
+        <v>0.0518</v>
       </c>
       <c r="H19" t="n">
-        <v>90.42106</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0.0532</v>
-      </c>
-      <c r="J19" t="n">
-        <v>1.91076</v>
+        <v>1.92674</v>
       </c>
     </row>
     <row r="20">
@@ -1044,54 +922,33 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>17.52518</v>
+        <v>17.587</v>
       </c>
       <c r="D20" t="n">
-        <v>17.10402</v>
+        <v>17.25912</v>
       </c>
       <c r="E20" t="n">
-        <v>17.60122</v>
+        <v>17.51603</v>
       </c>
       <c r="F20" t="n">
-        <v>58.02703</v>
+        <v>45.13446</v>
       </c>
       <c r="G20" t="n">
-        <v>44.2134</v>
+        <v>0.05319</v>
       </c>
       <c r="H20" t="n">
-        <v>88.88337</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0.05363</v>
-      </c>
-      <c r="J20" t="n">
-        <v>1.89762</v>
+        <v>1.92365</v>
       </c>
     </row>
     <row r="21">
       <c r="C21" t="inlineStr">
         <is>
-          <t>Max Stepheight</t>
+          <t>Dimple</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Min Stepheight</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Mean Stepheight</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Width</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Space</t>
+          <t>Bump</t>
         </is>
       </c>
     </row>
@@ -1103,23 +960,14 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Trace 1</t>
+          <t>via 1</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>17.52937</v>
+        <v>0.6399899999999999</v>
       </c>
       <c r="D22" t="n">
-        <v>16.83787</v>
-      </c>
-      <c r="E22" t="n">
-        <v>17.16331</v>
-      </c>
-      <c r="F22" t="n">
-        <v>23.2692</v>
-      </c>
-      <c r="G22" t="n">
-        <v>35.72825</v>
+        <v>1.18236</v>
       </c>
     </row>
     <row r="23">
@@ -1129,19 +977,10 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>17.64431</v>
+        <v>0.62761</v>
       </c>
       <c r="D23" t="n">
-        <v>16.39672</v>
-      </c>
-      <c r="E23" t="n">
-        <v>17.14195</v>
-      </c>
-      <c r="F23" t="n">
-        <v>23.33307</v>
-      </c>
-      <c r="G23" t="n">
-        <v>36.1929</v>
+        <v>1.15539</v>
       </c>
     </row>
     <row r="24">
@@ -1151,19 +990,10 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>17.722</v>
+        <v>0.63065</v>
       </c>
       <c r="D24" t="n">
-        <v>16.68862</v>
-      </c>
-      <c r="E24" t="n">
-        <v>17.2979</v>
-      </c>
-      <c r="F24" t="n">
-        <v>22.90096</v>
-      </c>
-      <c r="G24" t="n">
-        <v>36.38567</v>
+        <v>1.16969</v>
       </c>
     </row>
     <row r="25">
@@ -1173,19 +1003,10 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>17.39201</v>
+        <v>0.63617</v>
       </c>
       <c r="D25" t="n">
-        <v>16.65475</v>
-      </c>
-      <c r="E25" t="n">
-        <v>16.9927</v>
-      </c>
-      <c r="F25" t="n">
-        <v>22.9463</v>
-      </c>
-      <c r="G25" t="n">
-        <v>35.85292</v>
+        <v>1.16669</v>
       </c>
     </row>
     <row r="26">
@@ -1195,19 +1016,10 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>17.28415</v>
+        <v>0.64449</v>
       </c>
       <c r="D26" t="n">
-        <v>16.91609</v>
-      </c>
-      <c r="E26" t="n">
-        <v>17.12305</v>
-      </c>
-      <c r="F26" t="n">
-        <v>22.77397</v>
-      </c>
-      <c r="G26" t="n">
-        <v>35.89297</v>
+        <v>1.18561</v>
       </c>
     </row>
     <row r="27">
@@ -1217,19 +1029,10 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>17.63438</v>
+        <v>0.63007</v>
       </c>
       <c r="D27" t="n">
-        <v>17.00087</v>
-      </c>
-      <c r="E27" t="n">
-        <v>17.48706</v>
-      </c>
-      <c r="F27" t="n">
-        <v>23.01874</v>
-      </c>
-      <c r="G27" t="n">
-        <v>35.94382</v>
+        <v>1.14604</v>
       </c>
     </row>
     <row r="28">
@@ -1239,19 +1042,10 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>17.53729</v>
+        <v>0.62163</v>
       </c>
       <c r="D28" t="n">
-        <v>16.77986</v>
-      </c>
-      <c r="E28" t="n">
-        <v>17.03524</v>
-      </c>
-      <c r="F28" t="n">
-        <v>22.88195</v>
-      </c>
-      <c r="G28" t="n">
-        <v>35.98259</v>
+        <v>1.17309</v>
       </c>
     </row>
     <row r="29">
@@ -1261,19 +1055,10 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>17.75153</v>
+        <v>0.62752</v>
       </c>
       <c r="D29" t="n">
-        <v>16.34426</v>
-      </c>
-      <c r="E29" t="n">
-        <v>17.14932</v>
-      </c>
-      <c r="F29" t="n">
-        <v>22.94463</v>
-      </c>
-      <c r="G29" t="n">
-        <v>36.24012</v>
+        <v>1.14787</v>
       </c>
     </row>
     <row r="30">
@@ -1283,19 +1068,10 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>17.45298</v>
+        <v>0.63736</v>
       </c>
       <c r="D30" t="n">
-        <v>16.83526</v>
-      </c>
-      <c r="E30" t="n">
-        <v>17.29479</v>
-      </c>
-      <c r="F30" t="n">
-        <v>23.17618</v>
-      </c>
-      <c r="G30" t="n">
-        <v>36.26178</v>
+        <v>1.17432</v>
       </c>
     </row>
     <row r="31">
@@ -1352,28 +1128,28 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.7939000000000001</v>
+        <v>0.77751</v>
       </c>
       <c r="D32" t="n">
-        <v>0.08551</v>
+        <v>0.08516</v>
       </c>
       <c r="E32" t="n">
-        <v>0.64034</v>
+        <v>0.63995</v>
       </c>
       <c r="F32" t="n">
-        <v>1.02207</v>
+        <v>0.99509</v>
       </c>
       <c r="G32" t="n">
-        <v>0.1164</v>
+        <v>0.11469</v>
       </c>
       <c r="H32" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.007990000000000001</v>
       </c>
       <c r="I32" t="n">
-        <v>0.09719999999999999</v>
+        <v>0.09927999999999999</v>
       </c>
       <c r="J32" t="n">
-        <v>0.13483</v>
+        <v>0.1299</v>
       </c>
     </row>
     <row r="33">
@@ -1383,28 +1159,28 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.78882</v>
+        <v>0.775</v>
       </c>
       <c r="D33" t="n">
-        <v>0.08427999999999999</v>
+        <v>0.08617</v>
       </c>
       <c r="E33" t="n">
-        <v>0.63578</v>
+        <v>0.64851</v>
       </c>
       <c r="F33" t="n">
-        <v>1.01062</v>
+        <v>0.99965</v>
       </c>
       <c r="G33" t="n">
-        <v>0.11531</v>
+        <v>0.11437</v>
       </c>
       <c r="H33" t="n">
-        <v>0.007849999999999999</v>
+        <v>0.008059999999999999</v>
       </c>
       <c r="I33" t="n">
-        <v>0.09729</v>
+        <v>0.09598</v>
       </c>
       <c r="J33" t="n">
-        <v>0.13162</v>
+        <v>0.13122</v>
       </c>
     </row>
     <row r="34">
@@ -1414,28 +1190,28 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.79865</v>
+        <v>0.7917</v>
       </c>
       <c r="D34" t="n">
-        <v>0.08674</v>
+        <v>0.08449</v>
       </c>
       <c r="E34" t="n">
-        <v>0.6334</v>
+        <v>0.6412099999999999</v>
       </c>
       <c r="F34" t="n">
-        <v>1.01635</v>
+        <v>1.01245</v>
       </c>
       <c r="G34" t="n">
-        <v>0.11333</v>
+        <v>0.11332</v>
       </c>
       <c r="H34" t="n">
-        <v>0.008070000000000001</v>
+        <v>0.00788</v>
       </c>
       <c r="I34" t="n">
-        <v>0.09718</v>
+        <v>0.09773</v>
       </c>
       <c r="J34" t="n">
-        <v>0.13483</v>
+        <v>0.13063</v>
       </c>
     </row>
     <row r="35">
@@ -1445,28 +1221,28 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.78026</v>
+        <v>0.78038</v>
       </c>
       <c r="D35" t="n">
-        <v>0.08425000000000001</v>
+        <v>0.08393</v>
       </c>
       <c r="E35" t="n">
-        <v>0.63983</v>
+        <v>0.63209</v>
       </c>
       <c r="F35" t="n">
-        <v>1.01627</v>
+        <v>0.9999400000000001</v>
       </c>
       <c r="G35" t="n">
-        <v>0.11374</v>
+        <v>0.11332</v>
       </c>
       <c r="H35" t="n">
-        <v>0.00783</v>
+        <v>0.008019999999999999</v>
       </c>
       <c r="I35" t="n">
-        <v>0.09858</v>
+        <v>0.09804</v>
       </c>
       <c r="J35" t="n">
-        <v>0.12912</v>
+        <v>0.13013</v>
       </c>
     </row>
     <row r="36">
@@ -1476,28 +1252,28 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.78723</v>
+        <v>0.80116</v>
       </c>
       <c r="D36" t="n">
-        <v>0.08379</v>
+        <v>0.08457000000000001</v>
       </c>
       <c r="E36" t="n">
-        <v>0.65168</v>
+        <v>0.6206</v>
       </c>
       <c r="F36" t="n">
-        <v>1.01111</v>
+        <v>1.00091</v>
       </c>
       <c r="G36" t="n">
-        <v>0.11585</v>
+        <v>0.11449</v>
       </c>
       <c r="H36" t="n">
-        <v>0.007939999999999999</v>
+        <v>0.008189999999999999</v>
       </c>
       <c r="I36" t="n">
-        <v>0.09844</v>
+        <v>0.09758</v>
       </c>
       <c r="J36" t="n">
-        <v>0.13374</v>
+        <v>0.13316</v>
       </c>
     </row>
     <row r="37">
@@ -1507,28 +1283,28 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.78569</v>
+        <v>0.79784</v>
       </c>
       <c r="D37" t="n">
-        <v>0.08488999999999999</v>
+        <v>0.0859</v>
       </c>
       <c r="E37" t="n">
-        <v>0.63685</v>
+        <v>0.64178</v>
       </c>
       <c r="F37" t="n">
-        <v>1.01444</v>
+        <v>1.02262</v>
       </c>
       <c r="G37" t="n">
-        <v>0.11447</v>
+        <v>0.11492</v>
       </c>
       <c r="H37" t="n">
-        <v>0.00792</v>
+        <v>0.00796</v>
       </c>
       <c r="I37" t="n">
-        <v>0.09723999999999999</v>
+        <v>0.09712999999999999</v>
       </c>
       <c r="J37" t="n">
-        <v>0.13683</v>
+        <v>0.13037</v>
       </c>
     </row>
     <row r="38">
@@ -1538,28 +1314,28 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.78287</v>
+        <v>0.78939</v>
       </c>
       <c r="D38" t="n">
-        <v>0.08467</v>
+        <v>0.0844</v>
       </c>
       <c r="E38" t="n">
-        <v>0.63872</v>
+        <v>0.63162</v>
       </c>
       <c r="F38" t="n">
-        <v>0.99799</v>
+        <v>1.00523</v>
       </c>
       <c r="G38" t="n">
-        <v>0.11161</v>
+        <v>0.11583</v>
       </c>
       <c r="H38" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.00791</v>
       </c>
       <c r="I38" t="n">
-        <v>0.09582</v>
+        <v>0.09773999999999999</v>
       </c>
       <c r="J38" t="n">
-        <v>0.13413</v>
+        <v>0.13321</v>
       </c>
     </row>
     <row r="39">
@@ -1569,28 +1345,28 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.77638</v>
+        <v>0.784</v>
       </c>
       <c r="D39" t="n">
-        <v>0.08461</v>
+        <v>0.08658</v>
       </c>
       <c r="E39" t="n">
-        <v>0.63463</v>
+        <v>0.63423</v>
       </c>
       <c r="F39" t="n">
-        <v>1.00573</v>
+        <v>1.01588</v>
       </c>
       <c r="G39" t="n">
-        <v>0.1155</v>
+        <v>0.11208</v>
       </c>
       <c r="H39" t="n">
-        <v>0.007979999999999999</v>
+        <v>0.007939999999999999</v>
       </c>
       <c r="I39" t="n">
-        <v>0.09601999999999999</v>
+        <v>0.09984</v>
       </c>
       <c r="J39" t="n">
-        <v>0.13095</v>
+        <v>0.13385</v>
       </c>
     </row>
     <row r="40">
@@ -1600,28 +1376,28 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.78049</v>
+        <v>0.7948</v>
       </c>
       <c r="D40" t="n">
-        <v>0.08307</v>
+        <v>0.08450000000000001</v>
       </c>
       <c r="E40" t="n">
-        <v>0.62719</v>
+        <v>0.64066</v>
       </c>
       <c r="F40" t="n">
-        <v>1.0042</v>
+        <v>1.0119</v>
       </c>
       <c r="G40" t="n">
-        <v>0.11466</v>
+        <v>0.11626</v>
       </c>
       <c r="H40" t="n">
         <v>0.00791</v>
       </c>
       <c r="I40" t="n">
-        <v>0.09795</v>
+        <v>0.09698</v>
       </c>
       <c r="J40" t="n">
-        <v>0.13281</v>
+        <v>0.13112</v>
       </c>
     </row>
   </sheetData>
